--- a/artfynd/A 49380-2021 artfynd.xlsx
+++ b/artfynd/A 49380-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126441360</v>
       </c>
       <c r="B2" t="n">
-        <v>100534</v>
+        <v>100543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126441364</v>
       </c>
       <c r="B3" t="n">
-        <v>103794</v>
+        <v>103803</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126441367</v>
       </c>
       <c r="B4" t="n">
-        <v>100534</v>
+        <v>100543</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>126441362</v>
       </c>
       <c r="B5" t="n">
-        <v>103794</v>
+        <v>103803</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49380-2021 artfynd.xlsx
+++ b/artfynd/A 49380-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1101,6 +1101,118 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127739924</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58033</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nacksta, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>615288</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6920039</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Fågelinventering för Sundsvall kommun</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Jan Lindström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49380-2021 artfynd.xlsx
+++ b/artfynd/A 49380-2021 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>127739924</v>
       </c>
       <c r="B6" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49380-2021 artfynd.xlsx
+++ b/artfynd/A 49380-2021 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>127739924</v>
       </c>
       <c r="B6" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49380-2021 artfynd.xlsx
+++ b/artfynd/A 49380-2021 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>127739924</v>
       </c>
       <c r="B6" t="n">
-        <v>58042</v>
+        <v>58043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49380-2021 artfynd.xlsx
+++ b/artfynd/A 49380-2021 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>127739924</v>
       </c>
       <c r="B6" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49380-2021 artfynd.xlsx
+++ b/artfynd/A 49380-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126441360</v>
+        <v>126441358</v>
       </c>
       <c r="B2" t="n">
-        <v>100543</v>
+        <v>104628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>615281</v>
+        <v>615212</v>
       </c>
       <c r="R2" t="n">
-        <v>6920067</v>
+        <v>6919999</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126441364</v>
+        <v>127739924</v>
       </c>
       <c r="B3" t="n">
-        <v>103803</v>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +793,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nacksta V, Mpd</t>
+          <t>Nacksta, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615424</v>
+        <v>615288</v>
       </c>
       <c r="R3" t="n">
-        <v>6919908</v>
+        <v>6920039</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,22 +857,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>17:14</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:14</t>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fågelinventering för Sundsvall kommun</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +882,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Väg och Miljö AB, Jan Lindström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126441367</v>
+        <v>126441362</v>
       </c>
       <c r="B4" t="n">
-        <v>100543</v>
+        <v>104628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>615424</v>
+        <v>615445</v>
       </c>
       <c r="R4" t="n">
-        <v>6919908</v>
+        <v>6919949</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126441362</v>
+        <v>126441364</v>
       </c>
       <c r="B5" t="n">
-        <v>103803</v>
+        <v>104628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>615445</v>
+        <v>615424</v>
       </c>
       <c r="R5" t="n">
-        <v>6919949</v>
+        <v>6919908</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127739924</v>
+        <v>126441360</v>
       </c>
       <c r="B6" t="n">
-        <v>58055</v>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,47 +1119,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nacksta, Mpd</t>
+          <t>Nacksta V, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>615288</v>
+        <v>615281</v>
       </c>
       <c r="R6" t="n">
-        <v>6920039</v>
+        <v>6920067</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,17 +1173,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Fågelinventering för Sundsvall kommun</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,15 +1203,122 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Jan Lindström</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126441367</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nacksta V, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>615424</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6919908</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Selånger</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49380-2021 artfynd.xlsx
+++ b/artfynd/A 49380-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127739924</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126441358</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126441362</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126441364</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126441360</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,8 +1349,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126441367</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>